--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="226">
   <si>
     <t>Component list</t>
   </si>
@@ -694,6 +694,9 @@
   </si>
   <si>
     <t>LTE_MODULE_v2.0</t>
+  </si>
+  <si>
+    <t>JLCPCB</t>
   </si>
 </sst>
 </file>
@@ -908,7 +911,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1168,23 +1171,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1357,25 +1349,7 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1409,9 +1383,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1755,7 +1726,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1789,15 +1760,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="66"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1847,7 +1818,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="73"/>
+      <c r="S3" s="67"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1872,7 +1843,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="74"/>
+      <c r="S4" s="68"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1897,7 +1868,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="74"/>
+      <c r="S5" s="68"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1918,7 +1889,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="74"/>
+      <c r="S6" s="68"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1939,7 +1910,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="74"/>
+      <c r="S7" s="68"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1960,7 +1931,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="74"/>
+      <c r="S8" s="68"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2080,7 +2051,7 @@
     <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B44" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B43" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -2871,16 +2842,16 @@
       <c r="C25" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="D25" s="81" t="s">
+      <c r="D25" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="81" t="s">
+      <c r="E25" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="81" t="s">
+      <c r="F25" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="G25" s="81" t="s">
+      <c r="G25" s="64" t="s">
         <v>122</v>
       </c>
       <c r="H25" s="62" t="s">
@@ -2895,10 +2866,10 @@
       <c r="K25" s="62" t="s">
         <v>209</v>
       </c>
-      <c r="L25" s="81">
+      <c r="L25" s="64">
         <v>1</v>
       </c>
-      <c r="M25" s="81">
+      <c r="M25" s="64">
         <f t="shared" ref="M25" si="15">L25*5</f>
         <v>5</v>
       </c>
@@ -3557,11 +3528,15 @@
       <c r="H37" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="I37" s="51"/>
+      <c r="I37" s="51" t="s">
+        <v>209</v>
+      </c>
       <c r="J37" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="K37" s="51"/>
+      <c r="K37" s="51" t="s">
+        <v>209</v>
+      </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
@@ -3569,14 +3544,18 @@
         <f t="shared" ref="M37" si="26">L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="51"/>
-      <c r="O37" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="P37" s="52"/>
+      <c r="N37" s="51">
+        <v>6</v>
+      </c>
+      <c r="O37" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="P37" s="52">
+        <v>27.036000000000001</v>
+      </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="27">P37*N37</f>
-        <v>0</v>
+        <v>162.21600000000001</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
@@ -3683,10 +3662,12 @@
       <c r="O39" s="61" t="s">
         <v>218</v>
       </c>
-      <c r="P39" s="52"/>
+      <c r="P39" s="52">
+        <v>12</v>
+      </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="29">P39*N39</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
@@ -3865,7 +3846,9 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="54"/>
+      <c r="C43" s="54" t="s">
+        <v>220</v>
+      </c>
       <c r="D43" s="51"/>
       <c r="E43" s="51"/>
       <c r="F43" s="51"/>
@@ -3883,89 +3866,65 @@
       <c r="R43" s="51"/>
       <c r="S43" s="39"/>
     </row>
-    <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="47">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
-      <c r="N44" s="66"/>
-      <c r="O44" s="67"/>
-      <c r="P44" s="68"/>
-      <c r="Q44" s="69"/>
-      <c r="R44" s="65"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="45"/>
+      <c r="N44" s="73" t="s">
+        <v>5</v>
+      </c>
+      <c r="O44" s="74"/>
+      <c r="P44" s="74"/>
+      <c r="Q44" s="48">
+        <f>SUM(Q10:Q42)</f>
+        <v>274.35419999999993</v>
+      </c>
+      <c r="R44" s="69"/>
       <c r="S44" s="70"/>
     </row>
     <row r="45" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="40"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="45"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="79" t="s">
-        <v>5</v>
-      </c>
-      <c r="O45" s="80"/>
-      <c r="P45" s="80"/>
-      <c r="Q45" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>40.138199999999998</v>
-      </c>
-      <c r="R45" s="75"/>
-      <c r="S45" s="76"/>
-    </row>
-    <row r="46" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="79" t="s">
+      <c r="B45" s="25"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="O46" s="80"/>
-      <c r="P46" s="80"/>
-      <c r="Q46" s="49">
-        <f>Q45/5</f>
-        <v>8.0276399999999999</v>
-      </c>
-      <c r="R46" s="77"/>
-      <c r="S46" s="78"/>
+      <c r="O45" s="74"/>
+      <c r="P45" s="74"/>
+      <c r="Q45" s="49">
+        <f>Q44/5</f>
+        <v>54.870839999999987</v>
+      </c>
+      <c r="R45" s="71"/>
+      <c r="S45" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R45:S46"/>
+    <mergeCell ref="R44:S45"/>
+    <mergeCell ref="N44:P44"/>
     <mergeCell ref="N45:P45"/>
-    <mergeCell ref="N46:P46"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O11" r:id="rId1"/>
@@ -3998,9 +3957,10 @@
     <hyperlink ref="O23" r:id="rId28"/>
     <hyperlink ref="O42" r:id="rId29"/>
     <hyperlink ref="O39" r:id="rId30"/>
+    <hyperlink ref="O37" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
-  <drawing r:id="rId32"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
+  <drawing r:id="rId33"/>
 </worksheet>
 </file>
--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="228">
   <si>
     <t>Component list</t>
   </si>
@@ -168,9 +168,6 @@
     <t>R8, R11, R14, R18</t>
   </si>
   <si>
-    <t>R12, R15, R16</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -201,9 +198,6 @@
     <t>CAP CER 0.1UF 50V X5R 0603</t>
   </si>
   <si>
-    <t>220uF 5.4mm 10V 6.3mm ±20% SMD,D6.3xL5.4mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
-  </si>
-  <si>
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
@@ -228,9 +222,6 @@
     <t>6V 500mA 40A 1A 0603 Resettable Fuses ROHS</t>
   </si>
   <si>
-    <t>Sma Female Connector, Pcb Edge Mount Rohs Compliant: Yes</t>
-  </si>
-  <si>
     <t>PCI Express Mini Card (Mini PCIe)</t>
   </si>
   <si>
@@ -294,9 +285,6 @@
     <t>Cap-0402</t>
   </si>
   <si>
-    <t>RT1A221M0605</t>
-  </si>
-  <si>
     <t>cap-0402</t>
   </si>
   <si>
@@ -384,9 +372,6 @@
     <t>SMD0603-050</t>
   </si>
   <si>
-    <t>CON-SMA-EDGE-S</t>
-  </si>
-  <si>
     <t>POGO Connector 4 Pin</t>
   </si>
   <si>
@@ -447,9 +432,6 @@
     <t>Yageo</t>
   </si>
   <si>
-    <t>ROQANG</t>
-  </si>
-  <si>
     <t>TDK</t>
   </si>
   <si>
@@ -468,9 +450,6 @@
     <t>TECHFUSE</t>
   </si>
   <si>
-    <t>RF Solutions</t>
-  </si>
-  <si>
     <t>XKB Connectivity</t>
   </si>
   <si>
@@ -501,9 +480,6 @@
     <t>C59526</t>
   </si>
   <si>
-    <t>C267466</t>
-  </si>
-  <si>
     <t>C14664</t>
   </si>
   <si>
@@ -690,13 +666,43 @@
     <t>Aliexpress</t>
   </si>
   <si>
-    <t>Bill of Materials for Project [LTE_MODULE_v2.0.PrjPcb]</t>
-  </si>
-  <si>
     <t>LTE_MODULE_v2.0</t>
   </si>
   <si>
     <t>JLCPCB</t>
+  </si>
+  <si>
+    <t>1 Inner bore SMA Board Edge Bend -55℃~+155℃ 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
+  </si>
+  <si>
+    <t>HJ-SMA508</t>
+  </si>
+  <si>
+    <t>HJ Tech</t>
+  </si>
+  <si>
+    <t>C1509209</t>
+  </si>
+  <si>
+    <t>R12, R15, R16, R19, R20</t>
+  </si>
+  <si>
+    <t>CAP TANT 220UF 20% 6.3V SMD</t>
+  </si>
+  <si>
+    <t>Case-B</t>
+  </si>
+  <si>
+    <t>TLJB227M006R0500</t>
+  </si>
+  <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
+    <t>C30242</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [LTE_MODULE_v2.0.]</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1785,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1804,7 +1810,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1829,7 +1835,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1945,49 +1951,49 @@
         <v>22</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>199</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
@@ -2003,25 +2009,25 @@
         <v>23</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2034,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="P10" s="38">
         <v>0.45</v>
@@ -2044,7 +2050,7 @@
         <v>2.7</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="S10" s="50"/>
     </row>
@@ -2061,25 +2067,25 @@
         <v>24</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2092,7 +2098,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P11" s="52">
         <v>2.8999999999999998E-3</v>
@@ -2117,25 +2123,25 @@
         <v>25</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -2148,7 +2154,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P12" s="38">
         <v>1.6000000000000001E-3</v>
@@ -2173,25 +2179,25 @@
         <v>26</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G13" s="62" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="L13" s="51">
         <v>8</v>
@@ -2204,7 +2210,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P13" s="52">
         <v>2.3999999999999998E-3</v>
@@ -2216,7 +2222,7 @@
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2229,25 +2235,25 @@
         <v>27</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>60</v>
+        <v>222</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2257,17 +2263,17 @@
         <v>5</v>
       </c>
       <c r="N14" s="37">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P14" s="38">
-        <v>3.2399999999999998E-2</v>
+        <v>0.21779999999999999</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0.64799999999999991</v>
+        <v>2.1779999999999999</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -2285,25 +2291,25 @@
         <v>28</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -2316,7 +2322,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P15" s="52">
         <v>5.1999999999999998E-3</v>
@@ -2341,25 +2347,25 @@
         <v>29</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="L16" s="37">
         <v>3</v>
@@ -2372,7 +2378,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P16" s="38">
         <v>1E-3</v>
@@ -2397,25 +2403,25 @@
         <v>30</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2428,7 +2434,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P17" s="52">
         <v>1.41E-2</v>
@@ -2453,25 +2459,25 @@
         <v>31</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G18" s="62" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -2484,7 +2490,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P18" s="38">
         <v>0.1037</v>
@@ -2509,25 +2515,25 @@
         <v>32</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L19" s="51">
         <v>2</v>
@@ -2540,7 +2546,7 @@
         <v>20</v>
       </c>
       <c r="O19" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P19" s="52">
         <v>3.1699999999999999E-2</v>
@@ -2565,25 +2571,25 @@
         <v>33</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2596,7 +2602,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P20" s="38">
         <v>5.5599999999999997E-2</v>
@@ -2621,25 +2627,25 @@
         <v>34</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2652,7 +2658,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P21" s="52">
         <v>8.6400000000000005E-2</v>
@@ -2677,25 +2683,25 @@
         <v>35</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2708,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P22" s="38">
         <v>4.3200000000000002E-2</v>
@@ -2720,7 +2726,7 @@
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
     </row>
-    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="47">
         <f t="shared" si="0"/>
@@ -2733,25 +2739,25 @@
         <v>36</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -2764,18 +2770,16 @@
         <v>6</v>
       </c>
       <c r="O23" s="61" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="P23" s="52">
-        <v>1.69</v>
+        <v>0.8306</v>
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>10.14</v>
-      </c>
-      <c r="R23" s="63" t="s">
-        <v>219</v>
-      </c>
+        <v>4.9836</v>
+      </c>
+      <c r="R23" s="63"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2785,31 +2789,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D24" s="62" t="s">
         <v>37</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L24" s="62">
         <v>1</v>
@@ -2819,16 +2823,16 @@
         <v>5</v>
       </c>
       <c r="N24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="O24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="P24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Q24" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="R24" s="62"/>
       <c r="S24" s="59"/>
@@ -2846,25 +2850,25 @@
         <v>38</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F25" s="64" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G25" s="64" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L25" s="64">
         <v>1</v>
@@ -2874,16 +2878,16 @@
         <v>5</v>
       </c>
       <c r="N25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="O25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="P25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Q25" s="62" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -2901,25 +2905,25 @@
         <v>39</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -2932,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P26" s="38">
         <v>0.6714</v>
@@ -2957,25 +2961,25 @@
         <v>40</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -2988,7 +2992,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P27" s="52">
         <v>4.1000000000000003E-3</v>
@@ -3013,25 +3017,25 @@
         <v>41</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3044,7 +3048,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P28" s="38">
         <v>3.4799999999999998E-2</v>
@@ -3069,25 +3073,25 @@
         <v>42</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3100,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="O29" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P29" s="52">
         <v>5.1499999999999997E-2</v>
@@ -3125,25 +3129,25 @@
         <v>43</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L30" s="37">
         <v>4</v>
@@ -3156,7 +3160,7 @@
         <v>40</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P30" s="38">
         <v>3.3500000000000002E-2</v>
@@ -3181,25 +3185,25 @@
         <v>44</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="L31" s="51">
         <v>3</v>
@@ -3212,7 +3216,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P31" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3237,25 +3241,25 @@
         <v>45</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="L32" s="37">
         <v>2</v>
@@ -3268,7 +3272,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P32" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3293,25 +3297,25 @@
         <v>46</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="L33" s="51">
         <v>2</v>
@@ -3324,7 +3328,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P33" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3349,25 +3353,25 @@
         <v>47</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -3380,7 +3384,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P34" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3405,25 +3409,25 @@
         <v>48</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="L35" s="51">
         <v>4</v>
@@ -3436,7 +3440,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P35" s="52">
         <v>1.1000000000000001E-3</v>
@@ -3458,41 +3462,41 @@
         <v>19</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>49</v>
+        <v>221</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="L36" s="37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M36" s="37">
         <f>L36*5</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N36" s="37">
         <v>100</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P36" s="38">
         <v>1.5E-3</v>
@@ -3514,28 +3518,28 @@
         <v>20</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -3548,7 +3552,7 @@
         <v>6</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="P37" s="52">
         <v>27.036000000000001</v>
@@ -3570,28 +3574,28 @@
         <v>20</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L38" s="37">
         <v>1</v>
@@ -3604,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="O38" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P38" s="38">
         <v>0.64600000000000002</v>
@@ -3626,28 +3630,28 @@
         <v>20</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -3660,7 +3664,7 @@
         <v>6</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="P39" s="52">
         <v>12</v>
@@ -3682,28 +3686,28 @@
         <v>21</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -3716,7 +3720,7 @@
         <v>20</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P40" s="38">
         <v>3.85E-2</v>
@@ -3738,28 +3742,28 @@
         <v>20</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -3772,7 +3776,7 @@
         <v>6</v>
       </c>
       <c r="O41" s="61" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="P41" s="52">
         <v>0.43280000000000002</v>
@@ -3791,31 +3795,31 @@
         <v>33</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="I42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="J42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K42" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L42" s="51">
         <v>1</v>
@@ -3828,7 +3832,7 @@
         <v>6</v>
       </c>
       <c r="O42" s="61" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="P42" s="52">
         <v>1.02</v>
@@ -3847,7 +3851,7 @@
         <v>34</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D43" s="51"/>
       <c r="E43" s="51"/>
@@ -3887,7 +3891,7 @@
       <c r="P44" s="74"/>
       <c r="Q44" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>274.35419999999993</v>
+        <v>270.72779999999995</v>
       </c>
       <c r="R44" s="69"/>
       <c r="S44" s="70"/>
@@ -3913,7 +3917,7 @@
       <c r="P45" s="74"/>
       <c r="Q45" s="49">
         <f>Q44/5</f>
-        <v>54.870839999999987</v>
+        <v>54.145559999999989</v>
       </c>
       <c r="R45" s="71"/>
       <c r="S45" s="72"/>
@@ -3928,36 +3932,36 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O11" r:id="rId1"/>
-    <hyperlink ref="O14" r:id="rId2"/>
-    <hyperlink ref="O15" r:id="rId3"/>
-    <hyperlink ref="O16" r:id="rId4"/>
-    <hyperlink ref="O17" r:id="rId5"/>
-    <hyperlink ref="O19" r:id="rId6"/>
-    <hyperlink ref="O20" r:id="rId7"/>
-    <hyperlink ref="O21" r:id="rId8"/>
-    <hyperlink ref="O22" r:id="rId9"/>
-    <hyperlink ref="O26" r:id="rId10"/>
-    <hyperlink ref="O27" r:id="rId11"/>
-    <hyperlink ref="O28" r:id="rId12"/>
-    <hyperlink ref="O29" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O31" r:id="rId15"/>
-    <hyperlink ref="O32" r:id="rId16"/>
-    <hyperlink ref="O33" r:id="rId17"/>
-    <hyperlink ref="O34" r:id="rId18"/>
-    <hyperlink ref="O35" r:id="rId19"/>
-    <hyperlink ref="O36" r:id="rId20"/>
-    <hyperlink ref="O38" r:id="rId21"/>
-    <hyperlink ref="O40" r:id="rId22"/>
-    <hyperlink ref="O41" r:id="rId23"/>
-    <hyperlink ref="O12" r:id="rId24"/>
-    <hyperlink ref="O13" r:id="rId25"/>
-    <hyperlink ref="O18" r:id="rId26"/>
-    <hyperlink ref="O10" r:id="rId27"/>
-    <hyperlink ref="O23" r:id="rId28"/>
-    <hyperlink ref="O42" r:id="rId29"/>
-    <hyperlink ref="O39" r:id="rId30"/>
-    <hyperlink ref="O37" r:id="rId31"/>
+    <hyperlink ref="O15" r:id="rId2"/>
+    <hyperlink ref="O16" r:id="rId3"/>
+    <hyperlink ref="O17" r:id="rId4"/>
+    <hyperlink ref="O19" r:id="rId5"/>
+    <hyperlink ref="O20" r:id="rId6"/>
+    <hyperlink ref="O21" r:id="rId7"/>
+    <hyperlink ref="O22" r:id="rId8"/>
+    <hyperlink ref="O26" r:id="rId9"/>
+    <hyperlink ref="O27" r:id="rId10"/>
+    <hyperlink ref="O28" r:id="rId11"/>
+    <hyperlink ref="O29" r:id="rId12"/>
+    <hyperlink ref="O30" r:id="rId13"/>
+    <hyperlink ref="O31" r:id="rId14"/>
+    <hyperlink ref="O32" r:id="rId15"/>
+    <hyperlink ref="O33" r:id="rId16"/>
+    <hyperlink ref="O34" r:id="rId17"/>
+    <hyperlink ref="O35" r:id="rId18"/>
+    <hyperlink ref="O36" r:id="rId19"/>
+    <hyperlink ref="O38" r:id="rId20"/>
+    <hyperlink ref="O40" r:id="rId21"/>
+    <hyperlink ref="O41" r:id="rId22"/>
+    <hyperlink ref="O12" r:id="rId23"/>
+    <hyperlink ref="O13" r:id="rId24"/>
+    <hyperlink ref="O18" r:id="rId25"/>
+    <hyperlink ref="O10" r:id="rId26"/>
+    <hyperlink ref="O42" r:id="rId27"/>
+    <hyperlink ref="O39" r:id="rId28"/>
+    <hyperlink ref="O37" r:id="rId29"/>
+    <hyperlink ref="O23" r:id="rId30"/>
+    <hyperlink ref="O14" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>

--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -99,9 +99,6 @@
     <t>C2</t>
   </si>
   <si>
-    <t>C3, C4, C5, C11, C13, C15, C16, C17</t>
-  </si>
-  <si>
     <t>C6</t>
   </si>
   <si>
@@ -703,6 +700,9 @@
   </si>
   <si>
     <t>Bill of Materials for Project [LTE_MODULE_v2.0.]</t>
+  </si>
+  <si>
+    <t>C5, C11, C13, C15, C16, C17</t>
   </si>
 </sst>
 </file>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1951,49 +1951,49 @@
         <v>22</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="K9" s="30" t="s">
+      <c r="L9" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>196</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>198</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
@@ -2009,25 +2009,25 @@
         <v>23</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2040,7 +2040,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P10" s="38">
         <v>0.45</v>
@@ -2050,7 +2050,7 @@
         <v>2.7</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S10" s="50"/>
     </row>
@@ -2067,25 +2067,25 @@
         <v>24</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2098,7 +2098,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P11" s="52">
         <v>2.8999999999999998E-3</v>
@@ -2123,25 +2123,25 @@
         <v>25</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I12" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="J12" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>204</v>
-      </c>
       <c r="K12" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -2154,7 +2154,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P12" s="38">
         <v>1.6000000000000001E-3</v>
@@ -2176,41 +2176,41 @@
         <v>10</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I13" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="J13" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="J13" s="51" t="s">
-        <v>206</v>
-      </c>
       <c r="K13" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L13" s="51">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M13" s="51">
         <f t="shared" ref="M13" si="3">L13*5</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N13" s="51">
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P13" s="52">
         <v>2.3999999999999998E-3</v>
@@ -2232,28 +2232,28 @@
         <v>10</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="I14" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>226</v>
-      </c>
       <c r="K14" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2266,7 +2266,7 @@
         <v>10</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P14" s="38">
         <v>0.21779999999999999</v>
@@ -2288,28 +2288,28 @@
         <v>10</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -2322,7 +2322,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P15" s="52">
         <v>5.1999999999999998E-3</v>
@@ -2344,28 +2344,28 @@
         <v>10</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L16" s="37">
         <v>3</v>
@@ -2378,7 +2378,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P16" s="38">
         <v>1E-3</v>
@@ -2400,28 +2400,28 @@
         <v>10</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P17" s="52">
         <v>1.41E-2</v>
@@ -2456,28 +2456,28 @@
         <v>11</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G18" s="62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I18" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>208</v>
-      </c>
       <c r="K18" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -2490,7 +2490,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P18" s="38">
         <v>0.1037</v>
@@ -2512,28 +2512,28 @@
         <v>11</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L19" s="51">
         <v>2</v>
@@ -2546,7 +2546,7 @@
         <v>20</v>
       </c>
       <c r="O19" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P19" s="52">
         <v>3.1699999999999999E-2</v>
@@ -2568,28 +2568,28 @@
         <v>11</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2602,7 +2602,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P20" s="38">
         <v>5.5599999999999997E-2</v>
@@ -2624,28 +2624,28 @@
         <v>11</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2658,7 +2658,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P21" s="52">
         <v>8.6400000000000005E-2</v>
@@ -2680,28 +2680,28 @@
         <v>12</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2714,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P22" s="38">
         <v>4.3200000000000002E-2</v>
@@ -2736,28 +2736,28 @@
         <v>13</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="F23" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="G23" s="51" t="s">
+      <c r="H23" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="I23" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="I23" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
-      </c>
       <c r="K23" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -2770,7 +2770,7 @@
         <v>6</v>
       </c>
       <c r="O23" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P23" s="52">
         <v>0.8306</v>
@@ -2789,31 +2789,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L24" s="62">
         <v>1</v>
@@ -2823,16 +2823,16 @@
         <v>5</v>
       </c>
       <c r="N24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q24" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R24" s="62"/>
       <c r="S24" s="59"/>
@@ -2847,28 +2847,28 @@
         <v>14</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G25" s="64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L25" s="64">
         <v>1</v>
@@ -2878,16 +2878,16 @@
         <v>5</v>
       </c>
       <c r="N25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q25" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -2902,28 +2902,28 @@
         <v>15</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -2936,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P26" s="38">
         <v>0.6714</v>
@@ -2958,28 +2958,28 @@
         <v>16</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -2992,7 +2992,7 @@
         <v>100</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P27" s="52">
         <v>4.1000000000000003E-3</v>
@@ -3014,28 +3014,28 @@
         <v>17</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3048,7 +3048,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P28" s="38">
         <v>3.4799999999999998E-2</v>
@@ -3070,28 +3070,28 @@
         <v>17</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3104,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="O29" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P29" s="52">
         <v>5.1499999999999997E-2</v>
@@ -3126,28 +3126,28 @@
         <v>18</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L30" s="37">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>40</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P30" s="38">
         <v>3.3500000000000002E-2</v>
@@ -3182,28 +3182,28 @@
         <v>19</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L31" s="51">
         <v>3</v>
@@ -3216,7 +3216,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P31" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3238,28 +3238,28 @@
         <v>19</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L32" s="37">
         <v>2</v>
@@ -3272,7 +3272,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P32" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3294,28 +3294,28 @@
         <v>19</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L33" s="51">
         <v>2</v>
@@ -3328,7 +3328,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P33" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3350,28 +3350,28 @@
         <v>19</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -3384,7 +3384,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P34" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3406,28 +3406,28 @@
         <v>19</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L35" s="51">
         <v>4</v>
@@ -3440,7 +3440,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P35" s="52">
         <v>1.1000000000000001E-3</v>
@@ -3462,28 +3462,28 @@
         <v>19</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L36" s="37">
         <v>5</v>
@@ -3496,7 +3496,7 @@
         <v>100</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P36" s="38">
         <v>1.5E-3</v>
@@ -3518,28 +3518,28 @@
         <v>20</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         <v>6</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P37" s="52">
         <v>27.036000000000001</v>
@@ -3574,28 +3574,28 @@
         <v>20</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L38" s="37">
         <v>1</v>
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="O38" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P38" s="38">
         <v>0.64600000000000002</v>
@@ -3630,28 +3630,28 @@
         <v>20</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -3664,7 +3664,7 @@
         <v>6</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P39" s="52">
         <v>12</v>
@@ -3686,28 +3686,28 @@
         <v>21</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>20</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P40" s="38">
         <v>3.85E-2</v>
@@ -3742,28 +3742,28 @@
         <v>20</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         <v>6</v>
       </c>
       <c r="O41" s="61" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P41" s="52">
         <v>0.43280000000000002</v>
@@ -3795,31 +3795,31 @@
         <v>33</v>
       </c>
       <c r="C42" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="G42" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="D42" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="F42" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="G42" s="51" t="s">
-        <v>213</v>
-      </c>
       <c r="H42" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I42" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J42" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K42" s="51" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L42" s="51">
         <v>1</v>
@@ -3832,7 +3832,7 @@
         <v>6</v>
       </c>
       <c r="O42" s="61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P42" s="52">
         <v>1.02</v>
@@ -3851,7 +3851,7 @@
         <v>34</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D43" s="51"/>
       <c r="E43" s="51"/>
@@ -3890,7 +3890,7 @@
       <c r="O44" s="74"/>
       <c r="P44" s="74"/>
       <c r="Q44" s="48">
-        <f>SUM(Q10:Q42)</f>
+        <f>SUM(Q10:Q43)</f>
         <v>270.72779999999995</v>
       </c>
       <c r="R44" s="69"/>

--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="214">
   <si>
     <t>Component list</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Item Type</t>
   </si>
   <si>
-    <t>GNSS Antenna</t>
-  </si>
-  <si>
     <t>Capacitor</t>
   </si>
   <si>
@@ -69,15 +66,9 @@
     <t>SIM Card Connectors</t>
   </si>
   <si>
-    <t>Inductor</t>
-  </si>
-  <si>
     <t>LED</t>
   </si>
   <si>
-    <t>Mosfet</t>
-  </si>
-  <si>
     <t>Resistor</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>Ant1</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -135,12 +123,6 @@
     <t>J3</t>
   </si>
   <si>
-    <t>J4</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
     <t>LED1</t>
   </si>
   <si>
@@ -150,9 +132,6 @@
     <t>Q1, Q2, Q3, Q4</t>
   </si>
   <si>
-    <t>R1, R2, R4</t>
-  </si>
-  <si>
     <t>R3, R5</t>
   </si>
   <si>
@@ -171,24 +150,12 @@
     <t>U2</t>
   </si>
   <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
     <t>U5</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>1.584GHz GNSS Chip RF Antenna 1.559GHz ~ 1.609GHz 3.1dBi Solder Surface Mount</t>
-  </si>
-  <si>
-    <t>50V 4.3pF C0G 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
-  </si>
-  <si>
     <t>CAP CER 33PF 25V C0G/NP0 0402</t>
   </si>
   <si>
@@ -228,9 +195,6 @@
     <t>Copper Alloy Self bomb Gold plating 1.25mm Deck -40℃~+85℃ 260℃ NanoSIM SMD SIM Card Connectors ROHS</t>
   </si>
   <si>
-    <t>2nH ±0.3nH 0603 Inductors (SMD) ROHS</t>
-  </si>
-  <si>
     <t>Yellow-Green 572nm LED Indication - Discrete 2.05V 0603 (1608 Metric)</t>
   </si>
   <si>
@@ -264,9 +228,6 @@
     <t>IC SWITCH 4PDT 16MLP</t>
   </si>
   <si>
-    <t>GLOBAL IOT EMBEDDED SIM CHIP</t>
-  </si>
-  <si>
     <t>15V 5 Unidirectional 5V SOT-363 ESD Protection Devices ROHS</t>
   </si>
   <si>
@@ -303,9 +264,6 @@
     <t>XKNANO-113</t>
   </si>
   <si>
-    <t>IND-0603 (1608 Metric)</t>
-  </si>
-  <si>
     <t>LED-0603</t>
   </si>
   <si>
@@ -321,9 +279,6 @@
     <t>16-MLP (3x3)</t>
   </si>
   <si>
-    <t>QNF8 (6 x 5mm)</t>
-  </si>
-  <si>
     <t>SOT-363</t>
   </si>
   <si>
@@ -333,12 +288,6 @@
     <t>Manufacturer Part Number</t>
   </si>
   <si>
-    <t>SZC-C-1G18</t>
-  </si>
-  <si>
-    <t>0603CG4R3C500NT</t>
-  </si>
-  <si>
     <t>GRM1555C1E330JA01D</t>
   </si>
   <si>
@@ -372,9 +321,6 @@
     <t>POGO Connector 4 Pin</t>
   </si>
   <si>
-    <t>VHF160808H2N0ST</t>
-  </si>
-  <si>
     <t>19-21/G6C-FM1N2B/3T</t>
   </si>
   <si>
@@ -405,9 +351,6 @@
     <t>FSA2567MPX</t>
   </si>
   <si>
-    <t>SIM-ST-MFF2</t>
-  </si>
-  <si>
     <t>SMF05CT1G-ES</t>
   </si>
   <si>
@@ -417,12 +360,6 @@
     <t>Manufacturer</t>
   </si>
   <si>
-    <t>Synzen</t>
-  </si>
-  <si>
-    <t>FH</t>
-  </si>
-  <si>
     <t>Murata</t>
   </si>
   <si>
@@ -462,9 +399,6 @@
     <t>ON Semiconductor / Fairchild</t>
   </si>
   <si>
-    <t>Hologram</t>
-  </si>
-  <si>
     <t>ElecSuper</t>
   </si>
   <si>
@@ -474,9 +408,6 @@
     <t>LCSC Part Number</t>
   </si>
   <si>
-    <t>C59526</t>
-  </si>
-  <si>
     <t>C14664</t>
   </si>
   <si>
@@ -501,9 +432,6 @@
     <t>C381071</t>
   </si>
   <si>
-    <t>C395081</t>
-  </si>
-  <si>
     <t>C93689</t>
   </si>
   <si>
@@ -543,12 +471,6 @@
     <t>C2677366</t>
   </si>
   <si>
-    <t>1.559GHz ~ 1.609GHz</t>
-  </si>
-  <si>
-    <t>4.3pF</t>
-  </si>
-  <si>
     <t>33pF</t>
   </si>
   <si>
@@ -567,9 +489,6 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>2nH</t>
-  </si>
-  <si>
     <t>0R</t>
   </si>
   <si>
@@ -648,9 +567,6 @@
     <t>PCIE SMD PAD</t>
   </si>
   <si>
-    <t>Digikey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Not Available in LCSC </t>
   </si>
   <si>
@@ -681,9 +597,6 @@
     <t>C1509209</t>
   </si>
   <si>
-    <t>R12, R15, R16, R19, R20</t>
-  </si>
-  <si>
     <t>CAP TANT 220UF 20% 6.3V SMD</t>
   </si>
   <si>
@@ -703,6 +616,51 @@
   </si>
   <si>
     <t>C5, C11, C13, C15, C16, C17</t>
+  </si>
+  <si>
+    <t>Antenna</t>
+  </si>
+  <si>
+    <t>ANT1</t>
+  </si>
+  <si>
+    <t>RF ANT 1.575GHZ CHIP SOLDER SMD</t>
+  </si>
+  <si>
+    <t>W3011</t>
+  </si>
+  <si>
+    <t>Pulse</t>
+  </si>
+  <si>
+    <t>CAP CER 2.2PF 50V C0G/NPO 0603</t>
+  </si>
+  <si>
+    <t>CC0603CRNPO9BN2R2</t>
+  </si>
+  <si>
+    <t>C282246</t>
+  </si>
+  <si>
+    <t>2.2pF</t>
+  </si>
+  <si>
+    <t>J4, J5</t>
+  </si>
+  <si>
+    <t>R1, R2, R12, R15, R16, R19, R20</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>U3,U4</t>
+  </si>
+  <si>
+    <t>Transistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass Pipe </t>
   </si>
 </sst>
 </file>
@@ -1732,7 +1690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1785,7 +1743,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1810,7 +1768,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1835,7 +1793,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1948,87 +1906,85 @@
         <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>174</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="K10" s="37"/>
       <c r="L10" s="37">
         <v>1</v>
       </c>
@@ -2039,53 +1995,49 @@
       <c r="N10" s="37">
         <v>6</v>
       </c>
-      <c r="O10" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="P10" s="38">
-        <v>0.45</v>
-      </c>
+      <c r="O10" s="61"/>
+      <c r="P10" s="38"/>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="S10" s="50"/>
     </row>
-    <row r="11" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B43" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>105</v>
+        <v>205</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2094,18 +2046,12 @@
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>5</v>
       </c>
-      <c r="N11" s="51">
-        <v>100</v>
-      </c>
-      <c r="O11" s="60" t="s">
-        <v>201</v>
-      </c>
-      <c r="P11" s="52">
-        <v>2.8999999999999998E-3</v>
-      </c>
+      <c r="N11" s="51"/>
+      <c r="O11" s="60"/>
+      <c r="P11" s="52"/>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -2117,31 +2063,31 @@
         <v>3</v>
       </c>
       <c r="C12" s="54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -2154,7 +2100,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P12" s="38">
         <v>1.6000000000000001E-3</v>
@@ -2173,31 +2119,31 @@
         <v>4</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G13" s="62" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="L13" s="51">
         <v>6</v>
@@ -2210,7 +2156,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P13" s="52">
         <v>2.3999999999999998E-3</v>
@@ -2229,31 +2175,31 @@
         <v>5</v>
       </c>
       <c r="C14" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2266,7 +2212,7 @@
         <v>10</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P14" s="38">
         <v>0.21779999999999999</v>
@@ -2285,31 +2231,31 @@
         <v>6</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -2322,7 +2268,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P15" s="52">
         <v>5.1999999999999998E-3</v>
@@ -2341,31 +2287,31 @@
         <v>7</v>
       </c>
       <c r="C16" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="L16" s="37">
         <v>3</v>
@@ -2378,7 +2324,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P16" s="38">
         <v>1E-3</v>
@@ -2397,31 +2343,31 @@
         <v>8</v>
       </c>
       <c r="C17" s="54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2434,7 +2380,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P17" s="52">
         <v>1.41E-2</v>
@@ -2453,31 +2399,31 @@
         <v>9</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G18" s="62" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -2490,7 +2436,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P18" s="38">
         <v>0.1037</v>
@@ -2509,31 +2455,31 @@
         <v>10</v>
       </c>
       <c r="C19" s="54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L19" s="51">
         <v>2</v>
@@ -2546,7 +2492,7 @@
         <v>20</v>
       </c>
       <c r="O19" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P19" s="52">
         <v>3.1699999999999999E-2</v>
@@ -2565,31 +2511,31 @@
         <v>11</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2602,7 +2548,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P20" s="38">
         <v>5.5599999999999997E-2</v>
@@ -2621,31 +2567,31 @@
         <v>12</v>
       </c>
       <c r="C21" s="54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2658,7 +2604,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P21" s="52">
         <v>8.6400000000000005E-2</v>
@@ -2677,31 +2623,31 @@
         <v>13</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2714,7 +2660,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P22" s="38">
         <v>4.3200000000000002E-2</v>
@@ -2733,31 +2679,31 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -2770,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="O23" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P23" s="52">
         <v>0.8306</v>
@@ -2789,31 +2735,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="K24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L24" s="62">
         <v>1</v>
@@ -2823,16 +2769,16 @@
         <v>5</v>
       </c>
       <c r="N24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="O24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="P24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="Q24" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="R24" s="62"/>
       <c r="S24" s="59"/>
@@ -2844,31 +2790,31 @@
         <v>16</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="F25" s="64" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="G25" s="64" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L25" s="64">
         <v>1</v>
@@ -2878,16 +2824,16 @@
         <v>5</v>
       </c>
       <c r="N25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="O25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="P25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="Q25" s="62" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -2899,389 +2845,389 @@
         <v>17</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L26" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="37">
         <f>L26*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N26" s="37">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P26" s="38">
         <v>0.6714</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>4.0283999999999995</v>
+        <v>7.3853999999999997</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
     </row>
     <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="47">
-        <f t="shared" si="0"/>
+      <c r="B27" s="46">
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="H27" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="J27" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="K27" s="51" t="s">
-        <v>182</v>
-      </c>
-      <c r="L27" s="51">
+      <c r="C27" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J27" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="K27" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="37">
         <v>1</v>
       </c>
-      <c r="M27" s="51">
-        <f t="shared" ref="M27" si="16">L27*5</f>
+      <c r="M27" s="37">
+        <f>L27*5</f>
         <v>5</v>
       </c>
-      <c r="N27" s="51">
-        <v>100</v>
+      <c r="N27" s="37">
+        <v>20</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P27" s="52">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="Q27" s="52">
-        <f t="shared" ref="Q27" si="17">P27*N27</f>
-        <v>0.41000000000000003</v>
-      </c>
-      <c r="R27" s="51"/>
+        <v>174</v>
+      </c>
+      <c r="P27" s="38">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="Q27" s="38">
+        <f>P27*N27</f>
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="R27" s="37"/>
       <c r="S27" s="59"/>
     </row>
     <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="46">
-        <f>ROW(B28) - ROW($B$9)</f>
+      <c r="B28" s="47">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="37" t="s">
+      <c r="C28" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="I28" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="J28" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="K28" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L28" s="51">
+        <v>1</v>
+      </c>
+      <c r="M28" s="51">
+        <f t="shared" ref="M28" si="16">L28*5</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="51">
+        <v>10</v>
+      </c>
+      <c r="O28" s="61" t="s">
+        <v>174</v>
+      </c>
+      <c r="P28" s="52">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="Q28" s="52">
+        <f t="shared" ref="Q28" si="17">P28*N28</f>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="R28" s="51"/>
+      <c r="S28" s="59"/>
+    </row>
+    <row r="29" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="46">
+        <f>ROW(B29) - ROW($B$9)</f>
+        <v>20</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>212</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="L29" s="37">
+        <v>4</v>
+      </c>
+      <c r="M29" s="37">
+        <f>L29*5</f>
+        <v>20</v>
+      </c>
+      <c r="N29" s="37">
         <v>40</v>
       </c>
-      <c r="E28" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="I28" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="L28" s="37">
-        <v>1</v>
-      </c>
-      <c r="M28" s="37">
-        <f>L28*5</f>
-        <v>5</v>
-      </c>
-      <c r="N28" s="37">
-        <v>20</v>
-      </c>
-      <c r="O28" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P28" s="38">
-        <v>3.4799999999999998E-2</v>
-      </c>
-      <c r="Q28" s="38">
-        <f>P28*N28</f>
-        <v>0.69599999999999995</v>
-      </c>
-      <c r="R28" s="37"/>
-      <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="47">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="J29" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="K29" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="L29" s="51">
-        <v>1</v>
-      </c>
-      <c r="M29" s="51">
-        <f t="shared" ref="M29" si="18">L29*5</f>
-        <v>5</v>
-      </c>
-      <c r="N29" s="51">
-        <v>10</v>
-      </c>
       <c r="O29" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P29" s="52">
-        <v>5.1499999999999997E-2</v>
-      </c>
-      <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="19">P29*N29</f>
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="R29" s="51"/>
+        <v>174</v>
+      </c>
+      <c r="P29" s="38">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="Q29" s="38">
+        <f>P29*N29</f>
+        <v>1.34</v>
+      </c>
+      <c r="R29" s="37"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="L30" s="37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M30" s="37">
         <f>L30*5</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N30" s="37">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P30" s="38">
-        <v>3.3500000000000002E-2</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>1.34</v>
+        <v>0.15</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="47">
-        <f t="shared" si="0"/>
+      <c r="B31" s="46">
+        <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="I31" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="J31" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="K31" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="L31" s="51">
-        <v>3</v>
-      </c>
-      <c r="M31" s="51">
-        <f t="shared" ref="M31" si="20">L31*5</f>
-        <v>15</v>
-      </c>
-      <c r="N31" s="51">
+      <c r="C31" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="K31" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="L31" s="37">
+        <v>2</v>
+      </c>
+      <c r="M31" s="37">
+        <f>L31*5</f>
+        <v>10</v>
+      </c>
+      <c r="N31" s="37">
         <v>100</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P31" s="52">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="21">P31*N31</f>
-        <v>0.13</v>
-      </c>
-      <c r="R31" s="51"/>
+        <v>174</v>
+      </c>
+      <c r="P31" s="38">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q31" s="38">
+        <f>P31*N31</f>
+        <v>0.12</v>
+      </c>
+      <c r="R31" s="37"/>
       <c r="S31" s="59"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="46">
-        <f>ROW(B32) - ROW($B$9)</f>
+      <c r="B32" s="47">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="K32" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="L32" s="37">
-        <v>2</v>
-      </c>
-      <c r="M32" s="37">
-        <f>L32*5</f>
-        <v>10</v>
-      </c>
-      <c r="N32" s="37">
+      <c r="C32" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="G32" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="J32" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="K32" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L32" s="51">
+        <v>1</v>
+      </c>
+      <c r="M32" s="51">
+        <f t="shared" ref="M32" si="18">L32*5</f>
+        <v>5</v>
+      </c>
+      <c r="N32" s="51">
         <v>100</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P32" s="38">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q32" s="38">
-        <f>P32*N32</f>
-        <v>0.12</v>
-      </c>
-      <c r="R32" s="37"/>
+        <v>174</v>
+      </c>
+      <c r="P32" s="52">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q32" s="52">
+        <f t="shared" ref="Q32" si="19">P32*N32</f>
+        <v>0.13</v>
+      </c>
+      <c r="R32" s="51"/>
       <c r="S32" s="59"/>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
@@ -3291,50 +3237,50 @@
         <v>24</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="L33" s="51">
         <v>2</v>
       </c>
       <c r="M33" s="51">
-        <f t="shared" ref="M33" si="22">L33*5</f>
+        <f t="shared" ref="M33" si="20">L33*5</f>
         <v>10</v>
       </c>
       <c r="N33" s="51">
         <v>100</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P33" s="52">
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="23">P33*N33</f>
+        <f t="shared" ref="Q33" si="21">P33*N33</f>
         <v>0.13</v>
       </c>
       <c r="R33" s="51"/>
@@ -3347,31 +3293,31 @@
         <v>25</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -3384,7 +3330,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P34" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3403,165 +3349,165 @@
         <v>26</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="L35" s="51">
         <v>4</v>
       </c>
       <c r="M35" s="51">
-        <f t="shared" ref="M35" si="24">L35*5</f>
+        <f t="shared" ref="M35" si="22">L35*5</f>
         <v>20</v>
       </c>
       <c r="N35" s="51">
         <v>100</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P35" s="52">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="25">P35*N35</f>
+        <f t="shared" ref="Q35" si="23">P35*N35</f>
         <v>0.11</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="46">
-        <f>ROW(B36) - ROW($B$9)</f>
+      <c r="B36" s="47">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="L36" s="37">
+      <c r="C36" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="H36" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="I36" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="J36" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="K36" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L36" s="51">
+        <v>1</v>
+      </c>
+      <c r="M36" s="51">
+        <f t="shared" ref="M36" si="24">L36*5</f>
         <v>5</v>
       </c>
-      <c r="M36" s="37">
-        <f>L36*5</f>
-        <v>25</v>
-      </c>
-      <c r="N36" s="37">
-        <v>100</v>
+      <c r="N36" s="51">
+        <v>6</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P36" s="38">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q36" s="38">
-        <f>P36*N36</f>
-        <v>0.15</v>
-      </c>
-      <c r="R36" s="37"/>
+        <v>187</v>
+      </c>
+      <c r="P36" s="52">
+        <v>27.036000000000001</v>
+      </c>
+      <c r="Q36" s="52">
+        <f t="shared" ref="Q36" si="25">P36*N36</f>
+        <v>162.21600000000001</v>
+      </c>
+      <c r="R36" s="51"/>
       <c r="S36" s="59"/>
     </row>
     <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="47">
-        <f t="shared" si="0"/>
+      <c r="B37" s="46">
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="H37" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="I37" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="J37" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="K37" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="L37" s="51">
+      <c r="C37" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="H37" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J37" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="K37" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="L37" s="37">
         <v>1</v>
       </c>
-      <c r="M37" s="51">
-        <f t="shared" ref="M37" si="26">L37*5</f>
+      <c r="M37" s="37">
+        <f>L37*5</f>
         <v>5</v>
       </c>
-      <c r="N37" s="51">
+      <c r="N37" s="37">
         <v>6</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>215</v>
-      </c>
-      <c r="P37" s="52">
-        <v>27.036000000000001</v>
-      </c>
-      <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="27">P37*N37</f>
-        <v>162.21600000000001</v>
-      </c>
-      <c r="R37" s="51"/>
+        <v>174</v>
+      </c>
+      <c r="P37" s="38">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="Q37" s="38">
+        <f>P37*N37</f>
+        <v>3.8760000000000003</v>
+      </c>
+      <c r="R37" s="37"/>
       <c r="S37" s="59"/>
     </row>
     <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -3571,166 +3517,166 @@
         <v>29</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>49</v>
+        <v>211</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L38" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="37">
         <f>L38*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N38" s="37">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="O38" s="61" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P38" s="38">
-        <v>0.64600000000000002</v>
+        <v>3.85E-2</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>3.8760000000000003</v>
+        <v>0.77</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="47">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
       </c>
       <c r="M39" s="51">
-        <f t="shared" ref="M39" si="28">L39*5</f>
+        <f t="shared" ref="M39:M40" si="26">L39*5</f>
         <v>5</v>
       </c>
       <c r="N39" s="51">
         <v>6</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="P39" s="52">
-        <v>12</v>
+        <v>0.43280000000000002</v>
       </c>
       <c r="Q39" s="52">
-        <f t="shared" ref="Q39" si="29">P39*N39</f>
-        <v>72</v>
+        <f t="shared" ref="Q39:Q40" si="27">P39*N39</f>
+        <v>2.5968</v>
       </c>
       <c r="R39" s="51"/>
-      <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="S39" s="39"/>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="46">
-        <f>ROW(B40) - ROW($B$9)</f>
+      <c r="B40" s="47">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="K40" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="L40" s="37">
+      <c r="C40" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G40" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="H40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="J40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="K40" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="L40" s="51">
         <v>1</v>
       </c>
-      <c r="M40" s="37">
-        <f>L40*5</f>
+      <c r="M40" s="51">
+        <f t="shared" si="26"/>
         <v>5</v>
       </c>
-      <c r="N40" s="37">
-        <v>20</v>
+      <c r="N40" s="51">
+        <v>6</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P40" s="38">
-        <v>3.85E-2</v>
-      </c>
-      <c r="Q40" s="38">
-        <f>P40*N40</f>
-        <v>0.77</v>
-      </c>
-      <c r="R40" s="37"/>
-      <c r="S40" s="59"/>
+        <v>185</v>
+      </c>
+      <c r="P40" s="52">
+        <v>1.02</v>
+      </c>
+      <c r="Q40" s="52">
+        <f t="shared" si="27"/>
+        <v>6.12</v>
+      </c>
+      <c r="R40" s="51"/>
+      <c r="S40" s="39"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -3739,232 +3685,118 @@
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>102</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="H41" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="J41" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="K41" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="L41" s="51">
-        <v>1</v>
-      </c>
-      <c r="M41" s="51">
-        <f t="shared" ref="M41:M42" si="30">L41*5</f>
-        <v>5</v>
-      </c>
-      <c r="N41" s="51">
-        <v>6</v>
-      </c>
-      <c r="O41" s="61" t="s">
-        <v>201</v>
-      </c>
-      <c r="P41" s="52">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q41" s="52">
-        <f t="shared" ref="Q41:Q42" si="31">P41*N41</f>
-        <v>2.5968</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="51"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+      <c r="O41" s="61"/>
+      <c r="P41" s="52"/>
+      <c r="Q41" s="52"/>
       <c r="R41" s="51"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>211</v>
-      </c>
-      <c r="D42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="F42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="G42" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="H42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="I42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="J42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="K42" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="L42" s="51">
-        <v>1</v>
-      </c>
-      <c r="M42" s="51">
-        <f t="shared" si="30"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="N42" s="51">
+      <c r="O42" s="74"/>
+      <c r="P42" s="74"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>198.68480000000002</v>
+      </c>
+      <c r="R42" s="69"/>
+      <c r="S42" s="70"/>
+    </row>
+    <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="O42" s="61" t="s">
-        <v>213</v>
-      </c>
-      <c r="P42" s="52">
-        <v>1.02</v>
-      </c>
-      <c r="Q42" s="52">
-        <f t="shared" si="31"/>
-        <v>6.12</v>
-      </c>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
-    </row>
-    <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="47">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="54" t="s">
-        <v>211</v>
-      </c>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
-      <c r="K43" s="51"/>
-      <c r="L43" s="51"/>
-      <c r="M43" s="51"/>
-      <c r="N43" s="51"/>
-      <c r="O43" s="61"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="52"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="39"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="45"/>
-      <c r="M44" s="45"/>
-      <c r="N44" s="73" t="s">
-        <v>5</v>
-      </c>
-      <c r="O44" s="74"/>
-      <c r="P44" s="74"/>
-      <c r="Q44" s="48">
-        <f>SUM(Q10:Q43)</f>
-        <v>270.72779999999995</v>
-      </c>
-      <c r="R44" s="69"/>
-      <c r="S44" s="70"/>
-    </row>
-    <row r="45" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="73" t="s">
-        <v>6</v>
-      </c>
-      <c r="O45" s="74"/>
-      <c r="P45" s="74"/>
-      <c r="Q45" s="49">
-        <f>Q44/5</f>
-        <v>54.145559999999989</v>
-      </c>
-      <c r="R45" s="71"/>
-      <c r="S45" s="72"/>
+      <c r="O43" s="74"/>
+      <c r="P43" s="74"/>
+      <c r="Q43" s="49">
+        <f>Q42/5</f>
+        <v>39.736960000000003</v>
+      </c>
+      <c r="R43" s="71"/>
+      <c r="S43" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R44:S45"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O11" r:id="rId1"/>
-    <hyperlink ref="O15" r:id="rId2"/>
-    <hyperlink ref="O16" r:id="rId3"/>
-    <hyperlink ref="O17" r:id="rId4"/>
-    <hyperlink ref="O19" r:id="rId5"/>
-    <hyperlink ref="O20" r:id="rId6"/>
-    <hyperlink ref="O21" r:id="rId7"/>
-    <hyperlink ref="O22" r:id="rId8"/>
-    <hyperlink ref="O26" r:id="rId9"/>
-    <hyperlink ref="O27" r:id="rId10"/>
-    <hyperlink ref="O28" r:id="rId11"/>
-    <hyperlink ref="O29" r:id="rId12"/>
-    <hyperlink ref="O30" r:id="rId13"/>
-    <hyperlink ref="O31" r:id="rId14"/>
-    <hyperlink ref="O32" r:id="rId15"/>
-    <hyperlink ref="O33" r:id="rId16"/>
-    <hyperlink ref="O34" r:id="rId17"/>
-    <hyperlink ref="O35" r:id="rId18"/>
-    <hyperlink ref="O36" r:id="rId19"/>
-    <hyperlink ref="O38" r:id="rId20"/>
-    <hyperlink ref="O40" r:id="rId21"/>
-    <hyperlink ref="O41" r:id="rId22"/>
-    <hyperlink ref="O12" r:id="rId23"/>
-    <hyperlink ref="O13" r:id="rId24"/>
-    <hyperlink ref="O18" r:id="rId25"/>
-    <hyperlink ref="O10" r:id="rId26"/>
-    <hyperlink ref="O42" r:id="rId27"/>
-    <hyperlink ref="O39" r:id="rId28"/>
-    <hyperlink ref="O37" r:id="rId29"/>
-    <hyperlink ref="O23" r:id="rId30"/>
-    <hyperlink ref="O14" r:id="rId31"/>
+    <hyperlink ref="O15" r:id="rId1"/>
+    <hyperlink ref="O16" r:id="rId2"/>
+    <hyperlink ref="O17" r:id="rId3"/>
+    <hyperlink ref="O19" r:id="rId4"/>
+    <hyperlink ref="O20" r:id="rId5"/>
+    <hyperlink ref="O21" r:id="rId6"/>
+    <hyperlink ref="O22" r:id="rId7"/>
+    <hyperlink ref="O26" r:id="rId8"/>
+    <hyperlink ref="O27" r:id="rId9"/>
+    <hyperlink ref="O28" r:id="rId10"/>
+    <hyperlink ref="O29" r:id="rId11"/>
+    <hyperlink ref="O32" r:id="rId12"/>
+    <hyperlink ref="O31" r:id="rId13"/>
+    <hyperlink ref="O33" r:id="rId14"/>
+    <hyperlink ref="O34" r:id="rId15"/>
+    <hyperlink ref="O35" r:id="rId16"/>
+    <hyperlink ref="O30" r:id="rId17"/>
+    <hyperlink ref="O37" r:id="rId18"/>
+    <hyperlink ref="O38" r:id="rId19"/>
+    <hyperlink ref="O39" r:id="rId20"/>
+    <hyperlink ref="O12" r:id="rId21"/>
+    <hyperlink ref="O13" r:id="rId22"/>
+    <hyperlink ref="O18" r:id="rId23"/>
+    <hyperlink ref="O40" r:id="rId24"/>
+    <hyperlink ref="O36" r:id="rId25"/>
+    <hyperlink ref="O23" r:id="rId26"/>
+    <hyperlink ref="O14" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId32"/>
-  <drawing r:id="rId33"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
+  <drawing r:id="rId29"/>
 </worksheet>
 </file>
--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="215">
   <si>
     <t>Component list</t>
   </si>
@@ -661,6 +661,9 @@
   </si>
   <si>
     <t xml:space="preserve">Glass Pipe </t>
+  </si>
+  <si>
+    <t>Digikey</t>
   </si>
 </sst>
 </file>
@@ -1984,7 +1987,9 @@
       <c r="J10" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="K10" s="37"/>
+      <c r="K10" s="37" t="s">
+        <v>173</v>
+      </c>
       <c r="L10" s="37">
         <v>1</v>
       </c>
@@ -1995,11 +2000,15 @@
       <c r="N10" s="37">
         <v>6</v>
       </c>
-      <c r="O10" s="61"/>
-      <c r="P10" s="38"/>
+      <c r="O10" s="61" t="s">
+        <v>214</v>
+      </c>
+      <c r="P10" s="38">
+        <v>1.59</v>
+      </c>
       <c r="Q10" s="38">
         <f>P10*N10</f>
-        <v>0</v>
+        <v>9.5400000000000009</v>
       </c>
       <c r="R10" s="63" t="s">
         <v>182</v>
@@ -2046,12 +2055,18 @@
         <f t="shared" ref="M11" si="1">L11*5</f>
         <v>5</v>
       </c>
-      <c r="N11" s="51"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="52"/>
+      <c r="N11" s="51">
+        <v>100</v>
+      </c>
+      <c r="O11" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="P11" s="52">
+        <v>4.0000000000000001E-3</v>
+      </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="2">P11*N11</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -3727,7 +3742,7 @@
       <c r="P42" s="74"/>
       <c r="Q42" s="48">
         <f>SUM(Q10:Q41)</f>
-        <v>198.68480000000002</v>
+        <v>208.62480000000002</v>
       </c>
       <c r="R42" s="69"/>
       <c r="S42" s="70"/>
@@ -3753,7 +3768,7 @@
       <c r="P43" s="74"/>
       <c r="Q43" s="49">
         <f>Q42/5</f>
-        <v>39.736960000000003</v>
+        <v>41.724960000000003</v>
       </c>
       <c r="R43" s="71"/>
       <c r="S43" s="72"/>
@@ -3794,9 +3809,11 @@
     <hyperlink ref="O36" r:id="rId25"/>
     <hyperlink ref="O23" r:id="rId26"/>
     <hyperlink ref="O14" r:id="rId27"/>
+    <hyperlink ref="O10" r:id="rId28"/>
+    <hyperlink ref="O11" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
-  <drawing r:id="rId29"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -648,12 +648,6 @@
     <t>J4, J5</t>
   </si>
   <si>
-    <t>R1, R2, R12, R15, R16, R19, R20</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
     <t>U3,U4</t>
   </si>
   <si>
@@ -664,6 +658,12 @@
   </si>
   <si>
     <t>Digikey</t>
+  </si>
+  <si>
+    <t>R1, R2, R12</t>
+  </si>
+  <si>
+    <t>R4, R19</t>
   </si>
 </sst>
 </file>
@@ -2001,7 +2001,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P10" s="38">
         <v>1.59</v>
@@ -3028,7 +3028,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>36</v>
@@ -3087,7 +3087,7 @@
         <v>16</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>66</v>
@@ -3111,11 +3111,11 @@
         <v>161</v>
       </c>
       <c r="L30" s="37">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M30" s="37">
         <f>L30*5</f>
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="N30" s="37">
         <v>100</v>
@@ -3198,8 +3198,8 @@
       <c r="C32" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="51" t="s">
-        <v>210</v>
+      <c r="D32" s="37" t="s">
+        <v>214</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>61</v>
@@ -3223,11 +3223,11 @@
         <v>156</v>
       </c>
       <c r="L32" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="51">
         <f t="shared" ref="M32" si="18">L32*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N32" s="51">
         <v>100</v>
@@ -3535,7 +3535,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>69</v>
@@ -3706,7 +3706,7 @@
       <c r="E41" s="51"/>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H41" s="51"/>
       <c r="I41" s="51"/>

--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="221">
   <si>
     <t>Component list</t>
   </si>
@@ -573,12 +573,6 @@
     <t>Peripheral</t>
   </si>
   <si>
-    <t xml:space="preserve">SMA Male Antenna </t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
     <t>LTE_MODULE_v2.0</t>
   </si>
   <si>
@@ -664,6 +658,30 @@
   </si>
   <si>
     <t>R4, R19</t>
+  </si>
+  <si>
+    <t>2 5dBi 4GAntenna Vertical 2.4GHz 10W - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>801-4G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DreamLNK </t>
+  </si>
+  <si>
+    <t>C779858</t>
+  </si>
+  <si>
+    <t>BWGSMJWX105-7KJ</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>1.8 3dBi Vertical 50W - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>C497021</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1351,6 +1369,26 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1693,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1705,8 +1743,8 @@
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.140625" customWidth="1"/>
@@ -1746,7 +1784,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1771,7 +1809,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1796,7 +1834,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1964,22 +2002,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="37" t="s">
         <v>199</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>201</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>172</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>173</v>
@@ -2001,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P10" s="38">
         <v>1.59</v>
@@ -2018,7 +2056,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -2028,13 +2066,13 @@
         <v>20</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>72</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>114</v>
@@ -2043,10 +2081,10 @@
         <v>173</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2137,7 +2175,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>46</v>
@@ -2196,22 +2234,22 @@
         <v>22</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="G14" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>196</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>152</v>
@@ -2700,22 +2738,22 @@
         <v>31</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>172</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>189</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>191</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>173</v>
@@ -2863,7 +2901,7 @@
         <v>14</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>57</v>
@@ -3028,7 +3066,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>36</v>
@@ -3087,7 +3125,7 @@
         <v>16</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>66</v>
@@ -3199,7 +3237,7 @@
         <v>16</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>61</v>
@@ -3457,7 +3495,7 @@
         <v>6</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P36" s="52">
         <v>27.036000000000001</v>
@@ -3535,7 +3573,7 @@
         <v>18</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>69</v>
@@ -3618,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="51">
-        <f t="shared" ref="M39:M40" si="26">L39*5</f>
+        <f t="shared" ref="M39:M41" si="26">L39*5</f>
         <v>5</v>
       </c>
       <c r="N39" s="51">
@@ -3631,13 +3669,13 @@
         <v>0.43280000000000002</v>
       </c>
       <c r="Q39" s="52">
-        <f t="shared" ref="Q39:Q40" si="27">P39*N39</f>
+        <f t="shared" ref="Q39:Q41" si="27">P39*N39</f>
         <v>2.5968</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="39"/>
     </row>
-    <row r="40" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="47">
         <f t="shared" si="0"/>
@@ -3650,22 +3688,22 @@
         <v>173</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="F40" s="51" t="s">
         <v>173</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="H40" s="51" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="I40" s="51" t="s">
         <v>173</v>
       </c>
       <c r="J40" s="51" t="s">
-        <v>173</v>
+        <v>216</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>173</v>
@@ -3678,108 +3716,162 @@
         <v>5</v>
       </c>
       <c r="N40" s="51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="P40" s="52">
-        <v>1.02</v>
+        <v>1.8885000000000001</v>
       </c>
       <c r="Q40" s="52">
         <f t="shared" si="27"/>
-        <v>6.12</v>
+        <v>9.4425000000000008</v>
       </c>
       <c r="R40" s="51"/>
       <c r="S40" s="39"/>
     </row>
-    <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="47">
+    <row r="41" spans="1:19" s="82" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75"/>
+      <c r="B41" s="76">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="77" t="s">
         <v>183</v>
       </c>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51" t="s">
-        <v>211</v>
-      </c>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="51"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="61"/>
-      <c r="P41" s="52"/>
-      <c r="Q41" s="52"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="39"/>
-    </row>
-    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" s="78" t="s">
+        <v>219</v>
+      </c>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78" t="s">
+        <v>217</v>
+      </c>
+      <c r="H41" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="I41" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="J41" s="78" t="s">
+        <v>220</v>
+      </c>
+      <c r="K41" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="L41" s="78">
+        <v>1</v>
+      </c>
+      <c r="M41" s="78">
+        <f t="shared" si="26"/>
+        <v>5</v>
+      </c>
+      <c r="N41" s="78">
+        <v>5</v>
+      </c>
+      <c r="O41" s="79" t="s">
+        <v>174</v>
+      </c>
+      <c r="P41" s="80">
+        <v>1.0505</v>
+      </c>
+      <c r="Q41" s="52">
+        <f t="shared" si="27"/>
+        <v>5.2524999999999995</v>
+      </c>
+      <c r="R41" s="78"/>
+      <c r="S41" s="81"/>
+    </row>
+    <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="40"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="45"/>
-      <c r="M42" s="45"/>
-      <c r="N42" s="73" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="74"/>
-      <c r="P42" s="74"/>
-      <c r="Q42" s="48">
-        <f>SUM(Q10:Q41)</f>
-        <v>208.62480000000002</v>
-      </c>
-      <c r="R42" s="69"/>
-      <c r="S42" s="70"/>
+      <c r="B42" s="47">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="51"/>
+      <c r="M42" s="51"/>
+      <c r="N42" s="51"/>
+      <c r="O42" s="61"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="51"/>
+      <c r="S42" s="39"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45"/>
+      <c r="M43" s="45"/>
       <c r="N43" s="73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43" s="74"/>
       <c r="P43" s="74"/>
-      <c r="Q43" s="49">
-        <f>Q42/5</f>
-        <v>41.724960000000003</v>
-      </c>
-      <c r="R43" s="71"/>
-      <c r="S43" s="72"/>
+      <c r="Q43" s="48">
+        <f>SUM(Q10:Q42)</f>
+        <v>217.19980000000001</v>
+      </c>
+      <c r="R43" s="69"/>
+      <c r="S43" s="70"/>
+    </row>
+    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="73" t="s">
+        <v>6</v>
+      </c>
+      <c r="O44" s="74"/>
+      <c r="P44" s="74"/>
+      <c r="Q44" s="49">
+        <f>Q43/5</f>
+        <v>43.439959999999999</v>
+      </c>
+      <c r="R44" s="71"/>
+      <c r="S44" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R42:S43"/>
-    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R43:S44"/>
     <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
@@ -3805,15 +3897,16 @@
     <hyperlink ref="O12" r:id="rId21"/>
     <hyperlink ref="O13" r:id="rId22"/>
     <hyperlink ref="O18" r:id="rId23"/>
-    <hyperlink ref="O40" r:id="rId24"/>
-    <hyperlink ref="O36" r:id="rId25"/>
-    <hyperlink ref="O23" r:id="rId26"/>
-    <hyperlink ref="O14" r:id="rId27"/>
-    <hyperlink ref="O10" r:id="rId28"/>
-    <hyperlink ref="O11" r:id="rId29"/>
+    <hyperlink ref="O36" r:id="rId24"/>
+    <hyperlink ref="O23" r:id="rId25"/>
+    <hyperlink ref="O14" r:id="rId26"/>
+    <hyperlink ref="O10" r:id="rId27"/>
+    <hyperlink ref="O11" r:id="rId28"/>
+    <hyperlink ref="O40" r:id="rId29"/>
+    <hyperlink ref="O41" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
-  <drawing r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
+  <drawing r:id="rId32"/>
 </worksheet>
 </file>
--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="221">
   <si>
     <t>Component list</t>
   </si>
@@ -57,9 +57,6 @@
     <t>Fuse</t>
   </si>
   <si>
-    <t>Connector</t>
-  </si>
-  <si>
     <t>Pogo Connector</t>
   </si>
   <si>
@@ -579,18 +576,9 @@
     <t>JLCPCB</t>
   </si>
   <si>
-    <t>1 Inner bore SMA Board Edge Bend -55℃~+155℃ 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
-  </si>
-  <si>
-    <t>HJ-SMA508</t>
-  </si>
-  <si>
     <t>HJ Tech</t>
   </si>
   <si>
-    <t>C1509209</t>
-  </si>
-  <si>
     <t>CAP TANT 220UF 20% 6.3V SMD</t>
   </si>
   <si>
@@ -682,6 +670,18 @@
   </si>
   <si>
     <t>C497021</t>
+  </si>
+  <si>
+    <t>SMA Connector</t>
+  </si>
+  <si>
+    <t>1 Inner bore SMA Board Edge Bend 11mm 5.35mm Plugin RF Connectors / Coaxial Connectors ROHS</t>
+  </si>
+  <si>
+    <t>HJ-SMA175</t>
+  </si>
+  <si>
+    <t>C1509213</t>
   </si>
 </sst>
 </file>
@@ -1337,6 +1337,26 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1369,26 +1389,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1765,15 +1765,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="74"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1823,7 +1823,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="75"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1848,7 +1848,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="76"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1873,7 +1873,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="76"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1894,7 +1894,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="76"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1915,7 +1915,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="76"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1936,7 +1936,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="76"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1947,52 +1947,52 @@
         <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="K9" s="30" t="s">
+      <c r="L9" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>170</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -2002,31 +2002,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>201</v>
-      </c>
       <c r="I10" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="P10" s="38">
         <v>1.59</v>
@@ -2049,7 +2049,7 @@
         <v>9.5400000000000009</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S10" s="50"/>
     </row>
@@ -2063,28 +2063,28 @@
         <v>9</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         <v>100</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P11" s="52">
         <v>4.0000000000000001E-3</v>
@@ -2119,28 +2119,28 @@
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" s="62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I12" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="J12" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>176</v>
-      </c>
       <c r="K12" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -2153,7 +2153,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P12" s="38">
         <v>1.6000000000000001E-3</v>
@@ -2175,28 +2175,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I13" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="J13" s="51" t="s">
-        <v>178</v>
-      </c>
       <c r="K13" s="51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L13" s="51">
         <v>6</v>
@@ -2209,7 +2209,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P13" s="52">
         <v>2.3999999999999998E-3</v>
@@ -2231,28 +2231,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>194</v>
-      </c>
       <c r="K14" s="37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2265,7 +2265,7 @@
         <v>10</v>
       </c>
       <c r="O14" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P14" s="38">
         <v>0.21779999999999999</v>
@@ -2287,28 +2287,28 @@
         <v>9</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -2321,7 +2321,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P15" s="52">
         <v>5.1999999999999998E-3</v>
@@ -2343,28 +2343,28 @@
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L16" s="37">
         <v>3</v>
@@ -2377,7 +2377,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P16" s="38">
         <v>1E-3</v>
@@ -2399,28 +2399,28 @@
         <v>9</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2433,7 +2433,7 @@
         <v>50</v>
       </c>
       <c r="O17" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P17" s="52">
         <v>1.41E-2</v>
@@ -2455,28 +2455,28 @@
         <v>10</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I18" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="J18" s="37" t="s">
         <v>179</v>
       </c>
-      <c r="J18" s="37" t="s">
-        <v>180</v>
-      </c>
       <c r="K18" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -2489,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P18" s="38">
         <v>0.1037</v>
@@ -2511,28 +2511,28 @@
         <v>10</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L19" s="51">
         <v>2</v>
@@ -2545,7 +2545,7 @@
         <v>20</v>
       </c>
       <c r="O19" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P19" s="52">
         <v>3.1699999999999999E-2</v>
@@ -2567,28 +2567,28 @@
         <v>10</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2601,7 +2601,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P20" s="38">
         <v>5.5599999999999997E-2</v>
@@ -2623,28 +2623,28 @@
         <v>10</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2657,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P21" s="52">
         <v>8.6400000000000005E-2</v>
@@ -2679,28 +2679,28 @@
         <v>11</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P22" s="38">
         <v>4.3200000000000002E-2</v>
@@ -2732,32 +2732,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>12</v>
+        <v>217</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>173</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="I23" s="51"/>
       <c r="J23" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="K23" s="51" t="s">
-        <v>173</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="K23" s="51"/>
       <c r="L23" s="51">
         <v>1</v>
       </c>
@@ -2765,20 +2761,14 @@
         <f t="shared" ref="M23" si="13">L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="51">
-        <v>6</v>
-      </c>
-      <c r="O23" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="P23" s="52">
-        <v>0.8306</v>
-      </c>
+      <c r="N23" s="37"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="52"/>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>4.9836</v>
-      </c>
-      <c r="R23" s="63"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="51"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -2788,31 +2778,31 @@
         <v>15</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" s="62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F24" s="62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L24" s="62">
         <v>1</v>
@@ -2822,16 +2812,16 @@
         <v>5</v>
       </c>
       <c r="N24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q24" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R24" s="62"/>
       <c r="S24" s="59"/>
@@ -2843,31 +2833,31 @@
         <v>16</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F25" s="64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G25" s="64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L25" s="64">
         <v>1</v>
@@ -2877,16 +2867,16 @@
         <v>5</v>
       </c>
       <c r="N25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q25" s="62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -2898,31 +2888,31 @@
         <v>17</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L26" s="37">
         <v>2</v>
@@ -2935,7 +2925,7 @@
         <v>11</v>
       </c>
       <c r="O26" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P26" s="38">
         <v>0.6714</v>
@@ -2954,31 +2944,31 @@
         <v>18</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G27" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I27" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J27" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K27" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L27" s="37">
         <v>1</v>
@@ -2991,7 +2981,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P27" s="38">
         <v>3.4799999999999998E-2</v>
@@ -3010,31 +3000,31 @@
         <v>19</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F28" s="51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H28" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J28" s="51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L28" s="51">
         <v>1</v>
@@ -3047,7 +3037,7 @@
         <v>10</v>
       </c>
       <c r="O28" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P28" s="52">
         <v>5.1499999999999997E-2</v>
@@ -3066,31 +3056,31 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L29" s="37">
         <v>4</v>
@@ -3103,7 +3093,7 @@
         <v>40</v>
       </c>
       <c r="O29" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P29" s="38">
         <v>3.3500000000000002E-2</v>
@@ -3122,31 +3112,31 @@
         <v>21</v>
       </c>
       <c r="C30" s="53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L30" s="37">
         <v>3</v>
@@ -3159,7 +3149,7 @@
         <v>100</v>
       </c>
       <c r="O30" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P30" s="38">
         <v>1.5E-3</v>
@@ -3178,31 +3168,31 @@
         <v>22</v>
       </c>
       <c r="C31" s="53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L31" s="37">
         <v>2</v>
@@ -3215,7 +3205,7 @@
         <v>100</v>
       </c>
       <c r="O31" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P31" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3234,31 +3224,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E32" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G32" s="51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H32" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I32" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J32" s="51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L32" s="51">
         <v>2</v>
@@ -3271,7 +3261,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P32" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3290,31 +3280,31 @@
         <v>24</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" s="51">
         <v>2</v>
@@ -3327,7 +3317,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P33" s="52">
         <v>1.2999999999999999E-3</v>
@@ -3346,31 +3336,31 @@
         <v>25</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -3383,7 +3373,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P34" s="38">
         <v>1.1999999999999999E-3</v>
@@ -3402,31 +3392,31 @@
         <v>26</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L35" s="51">
         <v>4</v>
@@ -3439,7 +3429,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P35" s="52">
         <v>1.1000000000000001E-3</v>
@@ -3458,31 +3448,31 @@
         <v>27</v>
       </c>
       <c r="C36" s="54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G36" s="51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I36" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J36" s="51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L36" s="51">
         <v>1</v>
@@ -3495,7 +3485,7 @@
         <v>6</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P36" s="52">
         <v>27.036000000000001</v>
@@ -3514,31 +3504,31 @@
         <v>28</v>
       </c>
       <c r="C37" s="53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E37" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H37" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I37" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J37" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L37" s="37">
         <v>1</v>
@@ -3551,7 +3541,7 @@
         <v>6</v>
       </c>
       <c r="O37" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P37" s="38">
         <v>0.64600000000000002</v>
@@ -3570,31 +3560,31 @@
         <v>29</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L38" s="37">
         <v>2</v>
@@ -3607,7 +3597,7 @@
         <v>20</v>
       </c>
       <c r="O38" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P38" s="38">
         <v>3.85E-2</v>
@@ -3626,31 +3616,31 @@
         <v>30</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D39" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -3663,7 +3653,7 @@
         <v>6</v>
       </c>
       <c r="O39" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P39" s="52">
         <v>0.43280000000000002</v>
@@ -3682,31 +3672,31 @@
         <v>31</v>
       </c>
       <c r="C40" s="54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H40" s="51" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I40" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J40" s="51" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L40" s="51">
         <v>1</v>
@@ -3719,7 +3709,7 @@
         <v>5</v>
       </c>
       <c r="O40" s="61" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P40" s="52">
         <v>1.8885000000000001</v>
@@ -3731,59 +3721,59 @@
       <c r="R40" s="51"/>
       <c r="S40" s="39"/>
     </row>
-    <row r="41" spans="1:19" s="82" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="75"/>
-      <c r="B41" s="76">
+    <row r="41" spans="1:19" s="72" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="65"/>
+      <c r="B41" s="66">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="77" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="E41" s="78" t="s">
-        <v>219</v>
-      </c>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78" t="s">
-        <v>217</v>
-      </c>
-      <c r="H41" s="78" t="s">
-        <v>218</v>
-      </c>
-      <c r="I41" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="J41" s="78" t="s">
-        <v>220</v>
-      </c>
-      <c r="K41" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="L41" s="78">
+      <c r="C41" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="D41" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" s="68" t="s">
+        <v>215</v>
+      </c>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="H41" s="68" t="s">
+        <v>214</v>
+      </c>
+      <c r="I41" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="J41" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="K41" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="L41" s="68">
         <v>1</v>
       </c>
-      <c r="M41" s="78">
+      <c r="M41" s="68">
         <f t="shared" si="26"/>
         <v>5</v>
       </c>
-      <c r="N41" s="78">
+      <c r="N41" s="68">
         <v>5</v>
       </c>
-      <c r="O41" s="79" t="s">
-        <v>174</v>
-      </c>
-      <c r="P41" s="80">
+      <c r="O41" s="69" t="s">
+        <v>173</v>
+      </c>
+      <c r="P41" s="70">
         <v>1.0505</v>
       </c>
       <c r="Q41" s="52">
         <f t="shared" si="27"/>
         <v>5.2524999999999995</v>
       </c>
-      <c r="R41" s="78"/>
-      <c r="S41" s="81"/>
+      <c r="R41" s="68"/>
+      <c r="S41" s="71"/>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -3792,13 +3782,13 @@
         <v>33</v>
       </c>
       <c r="C42" s="54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D42" s="51"/>
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -3827,17 +3817,17 @@
       <c r="K43" s="45"/>
       <c r="L43" s="45"/>
       <c r="M43" s="45"/>
-      <c r="N43" s="73" t="s">
+      <c r="N43" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="74"/>
-      <c r="P43" s="74"/>
+      <c r="O43" s="82"/>
+      <c r="P43" s="82"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>217.19980000000001</v>
-      </c>
-      <c r="R43" s="69"/>
-      <c r="S43" s="70"/>
+        <v>212.21620000000001</v>
+      </c>
+      <c r="R43" s="77"/>
+      <c r="S43" s="78"/>
     </row>
     <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -3853,17 +3843,17 @@
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
       <c r="M44" s="10"/>
-      <c r="N44" s="73" t="s">
+      <c r="N44" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="O44" s="74"/>
-      <c r="P44" s="74"/>
+      <c r="O44" s="82"/>
+      <c r="P44" s="82"/>
       <c r="Q44" s="49">
         <f>Q43/5</f>
-        <v>43.439959999999999</v>
-      </c>
-      <c r="R44" s="71"/>
-      <c r="S44" s="72"/>
+        <v>42.443240000000003</v>
+      </c>
+      <c r="R44" s="79"/>
+      <c r="S44" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3898,7 +3888,7 @@
     <hyperlink ref="O13" r:id="rId22"/>
     <hyperlink ref="O18" r:id="rId23"/>
     <hyperlink ref="O36" r:id="rId24"/>
-    <hyperlink ref="O23" r:id="rId25"/>
+    <hyperlink ref="O23" r:id="rId25" display="LCSC"/>
     <hyperlink ref="O14" r:id="rId26"/>
     <hyperlink ref="O10" r:id="rId27"/>
     <hyperlink ref="O11" r:id="rId28"/>

--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="241">
   <si>
     <t>Component list</t>
   </si>
@@ -578,9 +578,6 @@
     <t>LTE_MODULE_v2.0</t>
   </si>
   <si>
-    <t>JLCPCB</t>
-  </si>
-  <si>
     <t>HJ Tech</t>
   </si>
   <si>
@@ -747,6 +744,9 @@
   </si>
   <si>
     <t>Total Cost (1000 Boards)</t>
+  </si>
+  <si>
+    <t>Chipsmall</t>
   </si>
 </sst>
 </file>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2346,22 +2346,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>196</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>197</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>172</v>
@@ -2383,7 +2383,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="38">
         <v>1.59</v>
@@ -2410,13 +2410,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>113</v>
@@ -2425,10 +2425,10 @@
         <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="K11" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2519,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>45</v>
@@ -2578,22 +2578,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>189</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>190</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>151</v>
@@ -3076,28 +3076,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -3245,7 +3245,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>56</v>
@@ -3410,7 +3410,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>35</v>
@@ -3469,7 +3469,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -3581,7 +3581,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -3795,7 +3795,7 @@
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -3823,7 +3823,7 @@
         <v>172</v>
       </c>
       <c r="J36" s="51" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K36" s="51" t="s">
         <v>172</v>
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="P36" s="52">
-        <v>27.036000000000001</v>
+        <v>62.987000000000002</v>
       </c>
       <c r="Q36" s="52">
         <f t="shared" ref="Q36" si="25">P36*N36</f>
-        <v>162.21600000000001</v>
+        <v>377.92200000000003</v>
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
@@ -3917,7 +3917,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>68</v>
@@ -4032,22 +4032,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>211</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -4088,20 +4088,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F41" s="68"/>
       <c r="G41" s="68" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="68" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="68" t="s">
-        <v>214</v>
-      </c>
       <c r="I41" s="68" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="68" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="68" t="s">
         <v>172</v>
@@ -4142,7 +4142,7 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -4178,7 +4178,7 @@
       <c r="P43" s="85"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>217.11340000000001</v>
+        <v>432.81939999999997</v>
       </c>
       <c r="R43" s="80"/>
       <c r="S43" s="81"/>
@@ -4204,7 +4204,7 @@
       <c r="P44" s="85"/>
       <c r="Q44" s="49">
         <f>Q43/5</f>
-        <v>43.42268</v>
+        <v>86.563879999999997</v>
       </c>
       <c r="R44" s="82"/>
       <c r="S44" s="83"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -4500,19 +4500,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>221</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>222</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>223</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>224</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -4528,22 +4528,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>196</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>197</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>172</v>
@@ -4565,7 +4565,7 @@
         <v>21</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="38">
         <v>1.431</v>
@@ -4592,13 +4592,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>113</v>
@@ -4607,10 +4607,10 @@
         <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="K11" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>45</v>
@@ -4760,22 +4760,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>189</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>190</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>151</v>
@@ -5258,28 +5258,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -5427,7 +5427,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>56</v>
@@ -5592,7 +5592,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>35</v>
@@ -5651,7 +5651,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -5763,7 +5763,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -5977,7 +5977,7 @@
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="75" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="75" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="73"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -6020,11 +6020,15 @@
       <c r="N36" s="51">
         <v>21</v>
       </c>
-      <c r="O36" s="61"/>
-      <c r="P36" s="52"/>
+      <c r="O36" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36" s="52">
+        <v>47.240250000000003</v>
+      </c>
       <c r="Q36" s="52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>992.04525000000012</v>
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
@@ -6095,7 +6099,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>68</v>
@@ -6210,22 +6214,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>211</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -6266,20 +6270,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>214</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -6320,7 +6324,7 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -6356,7 +6360,7 @@
       <c r="P43" s="85"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>151.11170000000001</v>
+        <v>1143.1569500000003</v>
       </c>
       <c r="R43" s="80"/>
       <c r="S43" s="81"/>
@@ -6382,7 +6386,7 @@
       <c r="P44" s="85"/>
       <c r="Q44" s="49">
         <f>Q43/20</f>
-        <v>7.5555850000000007</v>
+        <v>57.157847500000017</v>
       </c>
       <c r="R44" s="82"/>
       <c r="S44" s="83"/>
@@ -6425,9 +6429,10 @@
     <hyperlink ref="O40" r:id="rId27"/>
     <hyperlink ref="O41" r:id="rId28"/>
     <hyperlink ref="O23" r:id="rId29"/>
+    <hyperlink ref="O36" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
 
@@ -6486,7 +6491,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -6676,19 +6681,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>225</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>226</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>227</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>228</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -6704,22 +6709,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>196</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>197</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>172</v>
@@ -6741,7 +6746,7 @@
         <v>51</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="38">
         <v>1.35</v>
@@ -6768,13 +6773,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>113</v>
@@ -6783,10 +6788,10 @@
         <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="K11" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -6877,7 +6882,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>45</v>
@@ -6936,22 +6941,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>189</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>190</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>151</v>
@@ -7434,28 +7439,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
       </c>
       <c r="K23" s="51"/>
       <c r="L23" s="51">
@@ -7601,7 +7606,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>56</v>
@@ -7766,7 +7771,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>35</v>
@@ -7825,7 +7830,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -7937,7 +7942,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -8151,7 +8156,7 @@
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="75" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="75" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="73"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -8194,11 +8199,15 @@
       <c r="N36" s="51">
         <v>51</v>
       </c>
-      <c r="O36" s="61"/>
-      <c r="P36" s="52"/>
+      <c r="O36" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36" s="52">
+        <v>40.941549999999999</v>
+      </c>
       <c r="Q36" s="52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2088.0190499999999</v>
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
@@ -8269,7 +8278,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>68</v>
@@ -8384,22 +8393,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>211</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -8440,20 +8449,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>214</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -8494,7 +8503,7 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -8530,7 +8539,7 @@
       <c r="P43" s="85"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>328.23919999999998</v>
+        <v>2416.2582500000003</v>
       </c>
       <c r="R43" s="80"/>
       <c r="S43" s="81"/>
@@ -8556,7 +8565,7 @@
       <c r="P44" s="85"/>
       <c r="Q44" s="49">
         <f>Q43/50</f>
-        <v>6.5647839999999995</v>
+        <v>48.325165000000005</v>
       </c>
       <c r="R44" s="82"/>
       <c r="S44" s="83"/>
@@ -8599,9 +8608,10 @@
     <hyperlink ref="O40" r:id="rId27"/>
     <hyperlink ref="O41" r:id="rId28"/>
     <hyperlink ref="O23" r:id="rId29"/>
+    <hyperlink ref="O36" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
 
@@ -8660,7 +8670,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -8850,19 +8860,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>229</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>230</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>231</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>232</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -8878,22 +8888,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>196</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>197</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>172</v>
@@ -8915,7 +8925,7 @@
         <v>101</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="38">
         <v>1.1501999999999999</v>
@@ -8942,13 +8952,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>113</v>
@@ -8957,10 +8967,10 @@
         <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="K11" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -9051,7 +9061,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>45</v>
@@ -9110,22 +9120,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>189</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>190</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>151</v>
@@ -9608,28 +9618,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -9777,7 +9787,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>56</v>
@@ -9942,7 +9952,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>35</v>
@@ -10001,7 +10011,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -10113,7 +10123,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -10327,7 +10337,7 @@
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="75" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="75" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="73"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -10367,12 +10377,18 @@
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="N36" s="51"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="52"/>
+      <c r="N36" s="51">
+        <v>101</v>
+      </c>
+      <c r="O36" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36" s="52">
+        <v>36.21752</v>
+      </c>
       <c r="Q36" s="52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3657.9695200000001</v>
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
@@ -10443,7 +10459,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>68</v>
@@ -10558,22 +10574,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>211</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -10614,20 +10630,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>214</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -10668,7 +10684,7 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -10704,7 +10720,7 @@
       <c r="P43" s="85"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>594.2509</v>
+        <v>4252.2204199999996</v>
       </c>
       <c r="R43" s="80"/>
       <c r="S43" s="81"/>
@@ -10730,7 +10746,7 @@
       <c r="P44" s="85"/>
       <c r="Q44" s="49">
         <f>Q43/100</f>
-        <v>5.9425090000000003</v>
+        <v>42.522204199999997</v>
       </c>
       <c r="R44" s="82"/>
       <c r="S44" s="83"/>
@@ -10773,9 +10789,10 @@
     <hyperlink ref="O40" r:id="rId27"/>
     <hyperlink ref="O41" r:id="rId28"/>
     <hyperlink ref="O23" r:id="rId29"/>
+    <hyperlink ref="O36" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
 
@@ -10834,7 +10851,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -11024,19 +11041,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>233</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>234</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>235</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>236</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -11052,22 +11069,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>196</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>197</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>172</v>
@@ -11089,7 +11106,7 @@
         <v>501</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="38">
         <v>0.94499999999999995</v>
@@ -11116,13 +11133,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>113</v>
@@ -11131,10 +11148,10 @@
         <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="K11" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -11225,7 +11242,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>45</v>
@@ -11284,22 +11301,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>189</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>190</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>151</v>
@@ -11782,28 +11799,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -11951,7 +11968,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>56</v>
@@ -12116,7 +12133,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>35</v>
@@ -12175,7 +12192,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -12287,7 +12304,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -12501,7 +12518,7 @@
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="75" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="75" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="73"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -12541,14 +12558,18 @@
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="N36" s="51"/>
-      <c r="O36" s="61"/>
+      <c r="N36" s="51">
+        <v>501</v>
+      </c>
+      <c r="O36" s="61" t="s">
+        <v>240</v>
+      </c>
       <c r="P36" s="52">
-        <v>27.036000000000001</v>
+        <v>34.012979999999999</v>
       </c>
       <c r="Q36" s="52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>17040.502980000001</v>
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
@@ -12619,7 +12640,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>68</v>
@@ -12734,22 +12755,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>211</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -12790,20 +12811,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>214</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -12844,7 +12865,7 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -12880,7 +12901,7 @@
       <c r="P43" s="85"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>2686.9485999999997</v>
+        <v>19727.451580000001</v>
       </c>
       <c r="R43" s="80"/>
       <c r="S43" s="81"/>
@@ -12906,7 +12927,7 @@
       <c r="P44" s="85"/>
       <c r="Q44" s="49">
         <f>Q43/500</f>
-        <v>5.3738971999999992</v>
+        <v>39.454903160000001</v>
       </c>
       <c r="R44" s="82"/>
       <c r="S44" s="83"/>
@@ -12949,9 +12970,10 @@
     <hyperlink ref="O40" r:id="rId27"/>
     <hyperlink ref="O41" r:id="rId28"/>
     <hyperlink ref="O23" r:id="rId29"/>
+    <hyperlink ref="O36" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
 
@@ -13010,7 +13032,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -13200,19 +13222,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>237</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>238</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>239</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>240</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -13228,22 +13250,22 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="E10" s="37" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="37" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>171</v>
       </c>
       <c r="G10" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>196</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>197</v>
       </c>
       <c r="I10" s="37" t="s">
         <v>172</v>
@@ -13265,7 +13287,7 @@
         <v>1002</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P10" s="38">
         <v>0.78300000000000003</v>
@@ -13292,13 +13314,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F11" s="51" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>113</v>
@@ -13307,10 +13329,10 @@
         <v>172</v>
       </c>
       <c r="J11" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="K11" s="51" t="s">
         <v>200</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -13401,7 +13423,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E13" s="51" t="s">
         <v>45</v>
@@ -13460,22 +13482,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="G14" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="I14" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="37" t="s">
         <v>189</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="37" t="s">
-        <v>190</v>
       </c>
       <c r="K14" s="37" t="s">
         <v>151</v>
@@ -13958,28 +13980,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="51" t="s">
         <v>219</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>220</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -14127,7 +14149,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>56</v>
@@ -14292,7 +14314,7 @@
         <v>20</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D29" s="37" t="s">
         <v>35</v>
@@ -14351,7 +14373,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -14463,7 +14485,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -14677,7 +14699,7 @@
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" s="75" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" s="75" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="73"/>
       <c r="B36" s="47">
         <f t="shared" si="0"/>
@@ -14717,12 +14739,18 @@
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="N36" s="51"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="52"/>
+      <c r="N36" s="51">
+        <v>1001</v>
+      </c>
+      <c r="O36" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="P36" s="52">
+        <v>31.493500000000001</v>
+      </c>
       <c r="Q36" s="52">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>31524.9935</v>
       </c>
       <c r="R36" s="51"/>
       <c r="S36" s="59"/>
@@ -14793,7 +14821,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>68</v>
@@ -14908,22 +14936,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>211</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>212</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -14964,20 +14992,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>214</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -15018,7 +15046,7 @@
       <c r="E42" s="51"/>
       <c r="F42" s="51"/>
       <c r="G42" s="51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
@@ -15054,7 +15082,7 @@
       <c r="P43" s="85"/>
       <c r="Q43" s="48">
         <f>SUM(Q10:Q42)</f>
-        <v>5051.2368999999999</v>
+        <v>36576.230399999993</v>
       </c>
       <c r="R43" s="80"/>
       <c r="S43" s="81"/>
@@ -15080,7 +15108,7 @@
       <c r="P44" s="85"/>
       <c r="Q44" s="49">
         <f>Q43/1000</f>
-        <v>5.0512369000000001</v>
+        <v>36.576230399999993</v>
       </c>
       <c r="R44" s="82"/>
       <c r="S44" s="83"/>
@@ -15123,8 +15151,9 @@
     <hyperlink ref="O40" r:id="rId27"/>
     <hyperlink ref="O41" r:id="rId28"/>
     <hyperlink ref="O23" r:id="rId29"/>
+    <hyperlink ref="O36" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
--- a/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
+++ b/Design Files/LTE-Module-v2.0/BOM/eSpark_BOM_v2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="240">
   <si>
     <t>Component list</t>
   </si>
@@ -636,9 +636,6 @@
   </si>
   <si>
     <t>Transistor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glass Pipe </t>
   </si>
   <si>
     <t>Digikey</t>
@@ -2075,7 +2072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2383,7 +2380,7 @@
         <v>6</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P10" s="38">
         <v>1.59</v>
@@ -2400,7 +2397,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -3076,19 +3073,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>184</v>
@@ -3097,7 +3094,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -3469,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -3581,7 +3578,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -3839,7 +3836,7 @@
         <v>6</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="52">
         <v>62.987000000000002</v>
@@ -4032,22 +4029,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>210</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>211</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -4088,20 +4085,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F41" s="68"/>
       <c r="G41" s="68" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="68" t="s">
-        <v>213</v>
-      </c>
       <c r="I41" s="68" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K41" s="68" t="s">
         <v>172</v>
@@ -4129,93 +4126,65 @@
       <c r="R41" s="68"/>
       <c r="S41" s="71"/>
     </row>
-    <row r="42" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>432.81939999999997</v>
+      </c>
+      <c r="R42" s="80"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="85"/>
       <c r="P43" s="85"/>
-      <c r="Q43" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>432.81939999999997</v>
-      </c>
-      <c r="R43" s="80"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="49">
-        <f>Q43/5</f>
+      <c r="Q43" s="49">
+        <f>Q42/5</f>
         <v>86.563879999999997</v>
       </c>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R43:S44"/>
+    <mergeCell ref="R42:S43"/>
+    <mergeCell ref="N42:P42"/>
     <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
@@ -4257,7 +4226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -4500,19 +4469,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>220</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>221</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>222</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>223</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -4565,7 +4534,7 @@
         <v>21</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P10" s="38">
         <v>1.431</v>
@@ -4582,7 +4551,7 @@
     <row r="11" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="73"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -5258,19 +5227,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>184</v>
@@ -5279,7 +5248,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -5651,7 +5620,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -5763,7 +5732,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -6021,7 +5990,7 @@
         <v>21</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="52">
         <v>47.240250000000003</v>
@@ -6214,22 +6183,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>210</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>211</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -6270,20 +6239,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>213</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -6311,93 +6280,65 @@
       <c r="R41" s="51"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>1143.1569500000003</v>
+      </c>
+      <c r="R42" s="80"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="85"/>
       <c r="P43" s="85"/>
-      <c r="Q43" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>1143.1569500000003</v>
-      </c>
-      <c r="R43" s="80"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="49">
-        <f>Q43/20</f>
+      <c r="Q43" s="49">
+        <f>Q42/20</f>
         <v>57.157847500000017</v>
       </c>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
     <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S44"/>
-    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
@@ -6438,7 +6379,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -6681,19 +6622,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>224</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>225</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>226</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>227</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -6746,7 +6687,7 @@
         <v>51</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P10" s="38">
         <v>1.35</v>
@@ -6763,7 +6704,7 @@
     <row r="11" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="73"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -7439,19 +7380,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>184</v>
@@ -7460,7 +7401,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K23" s="51"/>
       <c r="L23" s="51">
@@ -7830,7 +7771,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -7942,7 +7883,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -8200,7 +8141,7 @@
         <v>51</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="52">
         <v>40.941549999999999</v>
@@ -8393,22 +8334,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>210</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>211</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -8449,20 +8390,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>213</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -8490,93 +8431,65 @@
       <c r="R41" s="51"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>2416.2582500000003</v>
+      </c>
+      <c r="R42" s="80"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="85"/>
       <c r="P43" s="85"/>
-      <c r="Q43" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>2416.2582500000003</v>
-      </c>
-      <c r="R43" s="80"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="49">
-        <f>Q43/50</f>
+      <c r="Q43" s="49">
+        <f>Q42/50</f>
         <v>48.325165000000005</v>
       </c>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
     <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S44"/>
-    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
@@ -8617,7 +8530,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -8860,19 +8773,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>228</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>229</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>230</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>231</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -8925,7 +8838,7 @@
         <v>101</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P10" s="38">
         <v>1.1501999999999999</v>
@@ -8942,7 +8855,7 @@
     <row r="11" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="73"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -9618,19 +9531,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>184</v>
@@ -9639,7 +9552,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -10011,7 +9924,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -10123,7 +10036,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -10381,7 +10294,7 @@
         <v>101</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="52">
         <v>36.21752</v>
@@ -10574,22 +10487,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>210</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>211</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -10630,20 +10543,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>213</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -10671,93 +10584,65 @@
       <c r="R41" s="51"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>4252.2204199999996</v>
+      </c>
+      <c r="R42" s="80"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="85"/>
       <c r="P43" s="85"/>
-      <c r="Q43" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>4252.2204199999996</v>
-      </c>
-      <c r="R43" s="80"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="49">
-        <f>Q43/100</f>
+      <c r="Q43" s="49">
+        <f>Q42/100</f>
         <v>42.522204199999997</v>
       </c>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
     <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S44"/>
-    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
@@ -10798,7 +10683,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -11041,19 +10926,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>232</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>233</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>234</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>235</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -11106,7 +10991,7 @@
         <v>501</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P10" s="38">
         <v>0.94499999999999995</v>
@@ -11123,7 +11008,7 @@
     <row r="11" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="73"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -11799,19 +11684,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>184</v>
@@ -11820,7 +11705,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -12192,7 +12077,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -12304,7 +12189,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -12562,7 +12447,7 @@
         <v>501</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="52">
         <v>34.012979999999999</v>
@@ -12755,22 +12640,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>210</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>211</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -12811,20 +12696,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>213</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -12852,93 +12737,65 @@
       <c r="R41" s="51"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>19727.451580000001</v>
+      </c>
+      <c r="R42" s="80"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="85"/>
       <c r="P43" s="85"/>
-      <c r="Q43" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>19727.451580000001</v>
-      </c>
-      <c r="R43" s="80"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="49">
-        <f>Q43/500</f>
+      <c r="Q43" s="49">
+        <f>Q42/500</f>
         <v>39.454903160000001</v>
       </c>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
     <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S44"/>
-    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
@@ -12979,7 +12836,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -13222,19 +13079,19 @@
         <v>161</v>
       </c>
       <c r="M9" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>236</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>237</v>
       </c>
       <c r="O9" s="30" t="s">
         <v>166</v>
       </c>
       <c r="P9" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>238</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>239</v>
       </c>
       <c r="R9" s="30" t="s">
         <v>169</v>
@@ -13287,7 +13144,7 @@
         <v>1002</v>
       </c>
       <c r="O10" s="61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P10" s="38">
         <v>0.78300000000000003</v>
@@ -13304,7 +13161,7 @@
     <row r="11" spans="1:19" s="75" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="73"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B42" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -13980,19 +13837,19 @@
         <v>14</v>
       </c>
       <c r="C23" s="54" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D23" s="51" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>171</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>184</v>
@@ -14001,7 +13858,7 @@
         <v>172</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>172</v>
@@ -14373,7 +14230,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E30" s="37" t="s">
         <v>65</v>
@@ -14485,7 +14342,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>60</v>
@@ -14743,7 +14600,7 @@
         <v>1001</v>
       </c>
       <c r="O36" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P36" s="52">
         <v>31.493500000000001</v>
@@ -14936,22 +14793,22 @@
         <v>172</v>
       </c>
       <c r="E40" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G40" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="51" t="s">
+      <c r="H40" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="I40" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J40" s="51" t="s">
         <v>210</v>
-      </c>
-      <c r="I40" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="51" t="s">
-        <v>211</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>172</v>
@@ -14992,20 +14849,20 @@
         <v>172</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F41" s="51"/>
       <c r="G41" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="51" t="s">
         <v>212</v>
       </c>
-      <c r="H41" s="51" t="s">
-        <v>213</v>
-      </c>
       <c r="I41" s="51" t="s">
         <v>172</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>172</v>
@@ -15033,93 +14890,65 @@
       <c r="R41" s="51"/>
       <c r="S41" s="39"/>
     </row>
-    <row r="42" spans="1:19" s="75" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="47">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="39"/>
+    <row r="42" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="84" t="s">
+        <v>5</v>
+      </c>
+      <c r="O42" s="85"/>
+      <c r="P42" s="85"/>
+      <c r="Q42" s="48">
+        <f>SUM(Q10:Q41)</f>
+        <v>36576.230399999993</v>
+      </c>
+      <c r="R42" s="80"/>
+      <c r="S42" s="81"/>
     </row>
     <row r="43" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="45"/>
-      <c r="M43" s="45"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
       <c r="N43" s="84" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O43" s="85"/>
       <c r="P43" s="85"/>
-      <c r="Q43" s="48">
-        <f>SUM(Q10:Q42)</f>
-        <v>36576.230399999993</v>
-      </c>
-      <c r="R43" s="80"/>
-      <c r="S43" s="81"/>
-    </row>
-    <row r="44" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="O44" s="85"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="49">
-        <f>Q43/1000</f>
+      <c r="Q43" s="49">
+        <f>Q42/1000</f>
         <v>36.576230399999993</v>
       </c>
-      <c r="R44" s="82"/>
-      <c r="S44" s="83"/>
+      <c r="R43" s="82"/>
+      <c r="S43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S43"/>
     <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S44"/>
-    <mergeCell ref="N44:P44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O15" r:id="rId1"/>
